--- a/May_5_full_log/LHS_HRP_0.0001_res.xlsx
+++ b/May_5_full_log/LHS_HRP_0.0001_res.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharm\Blueness\May_5_full_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28872CA8-43C8-45F2-A7A8-8E770A40E3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0665090A-9275-4080-9CC4-81CABAC9394B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>HRP</t>
+  </si>
   <si>
     <t>TMB</t>
   </si>
   <si>
     <t>H2O2</t>
+  </si>
+  <si>
+    <t>max_intensity</t>
+  </si>
+  <si>
+    <t>reaction_speed</t>
+  </si>
+  <si>
+    <t>color_retention</t>
   </si>
   <si>
     <t>AUC</t>
@@ -396,10 +408,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -409,362 +421,2966 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
+        <v>1E-4</v>
+      </c>
+      <c r="B2">
+        <v>0.263572637</v>
+      </c>
+      <c r="C2">
+        <v>0.32992663700000002</v>
+      </c>
+      <c r="D2">
+        <v>8.1243654822335003</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>568.6532994923864</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1E-4</v>
+      </c>
+      <c r="B3">
         <v>0.50619064000000003</v>
       </c>
-      <c r="B2">
+      <c r="C3">
         <v>0.23167289899999999</v>
       </c>
-      <c r="C2">
-        <v>3075.5930626057529</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="D3">
+        <v>6.5401015228426402</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>514.80101522842722</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1E-4</v>
+      </c>
+      <c r="B4">
+        <v>0.263572637</v>
+      </c>
+      <c r="C4">
+        <v>0.32992663700000002</v>
+      </c>
+      <c r="D4">
+        <v>7.0284263959391069</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>492.30786802030491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1E-4</v>
+      </c>
+      <c r="B5">
         <v>0.29278920899999999</v>
       </c>
-      <c r="B3">
+      <c r="C5">
         <v>0.107853238</v>
       </c>
-      <c r="C3">
-        <v>3061.9670050761429</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="D5">
+        <v>7.4857868020304608</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>480.19314720812162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1E-4</v>
+      </c>
+      <c r="B6">
+        <v>0.50619064000000003</v>
+      </c>
+      <c r="C6">
+        <v>0.23167289899999999</v>
+      </c>
+      <c r="D6">
+        <v>6.2218274111675029</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>465.62918781725909</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1E-4</v>
+      </c>
+      <c r="B7">
+        <v>0.90233605100000003</v>
+      </c>
+      <c r="C7">
+        <v>0.11827801</v>
+      </c>
+      <c r="D7">
+        <v>5.6040609137055668</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>457.93477157360451</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1E-4</v>
+      </c>
+      <c r="B8">
+        <v>0.29278920899999999</v>
+      </c>
+      <c r="C8">
+        <v>0.107853238</v>
+      </c>
+      <c r="D8">
+        <v>7.5873096446700643</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>454.10329949238599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1E-4</v>
+      </c>
+      <c r="B9">
         <v>0.184395579</v>
       </c>
-      <c r="B4">
+      <c r="C9">
         <v>0.45432517300000003</v>
       </c>
-      <c r="C4">
-        <v>3013.8422165820639</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="D9">
+        <v>6.5274111675127173</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>448.74873096446748</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1E-4</v>
+      </c>
+      <c r="B10">
+        <v>0.29278920899999999</v>
+      </c>
+      <c r="C10">
+        <v>0.107853238</v>
+      </c>
+      <c r="D10">
+        <v>7.4081218274111862</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>446.87817258883331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1E-4</v>
+      </c>
+      <c r="B11">
+        <v>0.184395579</v>
+      </c>
+      <c r="C11">
+        <v>0.45432517300000003</v>
+      </c>
+      <c r="D11">
+        <v>5.9664974619289204</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>445.11015228426402</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1E-4</v>
+      </c>
+      <c r="B12">
+        <v>0.29278920899999999</v>
+      </c>
+      <c r="C12">
+        <v>0.107853238</v>
+      </c>
+      <c r="D12">
+        <v>7.2192893401015246</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>433.94619289340119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1E-4</v>
+      </c>
+      <c r="B13">
+        <v>0.90233605100000003</v>
+      </c>
+      <c r="C13">
+        <v>0.11827801</v>
+      </c>
+      <c r="D13">
+        <v>5.3786802030456968</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>428.40329949238662</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>1E-4</v>
+      </c>
+      <c r="B14">
+        <v>0.50619064000000003</v>
+      </c>
+      <c r="C14">
+        <v>0.23167289899999999</v>
+      </c>
+      <c r="D14">
+        <v>5.6614213197969647</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>393.85406091370572</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1E-4</v>
+      </c>
+      <c r="B15">
+        <v>0.36182264400000003</v>
+      </c>
+      <c r="C15">
+        <v>5.3704440000000003E-3</v>
+      </c>
+      <c r="D15">
+        <v>6.6167512690355386</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>379.37385786802088</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1E-4</v>
+      </c>
+      <c r="B16">
+        <v>0.61440889099999996</v>
+      </c>
+      <c r="C16">
+        <v>1.3667955000000001E-2</v>
+      </c>
+      <c r="D16">
+        <v>7.6020304568527806</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>376.34314720812188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1E-4</v>
+      </c>
+      <c r="B17">
         <v>0.263572637</v>
       </c>
-      <c r="B5">
+      <c r="C17">
         <v>0.32992663700000002</v>
       </c>
-      <c r="C5">
-        <v>3009.8582910321488</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="D17">
+        <v>5.4979695431472244</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>365.79644670050823</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>1E-4</v>
+      </c>
+      <c r="B18">
+        <v>5.5845456000000002E-2</v>
+      </c>
+      <c r="C18">
+        <v>1.9363977000000001E-2</v>
+      </c>
+      <c r="D18">
+        <v>4.9431472081218386</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>353.68807106599053</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1E-4</v>
+      </c>
+      <c r="B19">
+        <v>0.36182264400000003</v>
+      </c>
+      <c r="C19">
+        <v>5.3704440000000003E-3</v>
+      </c>
+      <c r="D19">
+        <v>6.1426395939086396</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>346.40812182741172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>1E-4</v>
+      </c>
+      <c r="B20">
+        <v>5.5845456000000002E-2</v>
+      </c>
+      <c r="C20">
+        <v>1.9363977000000001E-2</v>
+      </c>
+      <c r="D20">
+        <v>4.7279187817258546</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>320.11015228426407</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>1E-4</v>
+      </c>
+      <c r="B21">
+        <v>0.263572637</v>
+      </c>
+      <c r="C21">
+        <v>0.32992663700000002</v>
+      </c>
+      <c r="D21">
+        <v>4.7766497461928807</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>319.51954314720911</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>1E-4</v>
+      </c>
+      <c r="B22">
+        <v>0.50619064000000003</v>
+      </c>
+      <c r="C22">
+        <v>0.23167289899999999</v>
+      </c>
+      <c r="D22">
+        <v>4.6736040609137213</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>318.80152284264</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>1E-4</v>
+      </c>
+      <c r="B23">
+        <v>0.61440889099999996</v>
+      </c>
+      <c r="C23">
+        <v>1.3667955000000001E-2</v>
+      </c>
+      <c r="D23">
+        <v>6.7335025380710816</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>314.97182741116751</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>1E-4</v>
+      </c>
+      <c r="B24">
+        <v>0.184395579</v>
+      </c>
+      <c r="C24">
+        <v>0.45432517300000003</v>
+      </c>
+      <c r="D24">
+        <v>4.1883248730964411</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>296.28959390863002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>1E-4</v>
+      </c>
+      <c r="B25">
         <v>0.90233605100000003</v>
       </c>
-      <c r="B6">
+      <c r="C25">
         <v>0.11827801</v>
       </c>
-      <c r="C6">
-        <v>2945.0241116751281</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="D25">
+        <v>3.6411167512690379</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>291.12208121827467</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>1E-4</v>
+      </c>
+      <c r="B26">
+        <v>0.105007356</v>
+      </c>
+      <c r="C26">
+        <v>0.60413150599999998</v>
+      </c>
+      <c r="D26">
+        <v>4.9314720812182777</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>286.13883248731042</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>1E-4</v>
+      </c>
+      <c r="B27">
         <v>5.5845456000000002E-2</v>
       </c>
-      <c r="B7">
+      <c r="C27">
         <v>1.9363977000000001E-2</v>
       </c>
-      <c r="C7">
-        <v>2936.2580372250432</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="D27">
+        <v>4.2736040609136801</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>284.19619289340142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>1E-4</v>
+      </c>
+      <c r="B28">
         <v>0.105007356</v>
       </c>
-      <c r="B8">
+      <c r="C28">
         <v>0.60413150599999998</v>
       </c>
-      <c r="C8">
-        <v>2883.868443316414</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9">
+      <c r="D28">
+        <v>4.4736040609137264</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>271.82030456852868</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>1E-4</v>
+      </c>
+      <c r="B29">
+        <v>0.90233605100000003</v>
+      </c>
+      <c r="C29">
+        <v>0.11827801</v>
+      </c>
+      <c r="D29">
+        <v>3.2482233502538018</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>263.51370558375697</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>1E-4</v>
+      </c>
+      <c r="B30">
         <v>0.61440889099999996</v>
       </c>
-      <c r="B9">
+      <c r="C30">
         <v>1.3667955000000001E-2</v>
       </c>
-      <c r="C9">
-        <v>2880.8164128595599</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10">
+      <c r="D30">
+        <v>6.309137055837585</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>259.41675126903613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>1E-4</v>
+      </c>
+      <c r="B31">
+        <v>5.5845456000000002E-2</v>
+      </c>
+      <c r="C31">
+        <v>1.9363977000000001E-2</v>
+      </c>
+      <c r="D31">
+        <v>3.2568527918781811</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>247.32868020304619</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>1E-4</v>
+      </c>
+      <c r="B32">
+        <v>0.38977679199999998</v>
+      </c>
+      <c r="C32">
+        <v>0.21193631600000001</v>
+      </c>
+      <c r="D32">
+        <v>3.5781725888324618</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>244.67055837563419</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>1E-4</v>
+      </c>
+      <c r="B33">
+        <v>0.105007356</v>
+      </c>
+      <c r="C33">
+        <v>0.60413150599999998</v>
+      </c>
+      <c r="D33">
+        <v>3.8888324873096418</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>241.52487309644789</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>1E-4</v>
+      </c>
+      <c r="B34">
         <v>0.36182264400000003</v>
       </c>
-      <c r="B10">
+      <c r="C34">
         <v>5.3704440000000003E-3</v>
       </c>
-      <c r="C10">
-        <v>2878.4813874788501</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="D34">
+        <v>4.6847715736040598</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>222.85812182741179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>1E-4</v>
+      </c>
+      <c r="B35">
+        <v>0.61440889099999996</v>
+      </c>
+      <c r="C35">
+        <v>1.3667955000000001E-2</v>
+      </c>
+      <c r="D35">
+        <v>6.1817258883248591</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>215.18426395939119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>1E-4</v>
+      </c>
+      <c r="B36">
+        <v>0.36182264400000003</v>
+      </c>
+      <c r="C36">
+        <v>5.3704440000000003E-3</v>
+      </c>
+      <c r="D36">
+        <v>4.3979695431472017</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>213.95659898477129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>1E-4</v>
+      </c>
+      <c r="B37">
+        <v>0.12010299200000001</v>
+      </c>
+      <c r="C37">
+        <v>1.6509238999999998E-2</v>
+      </c>
+      <c r="D37">
+        <v>2.3472081218274208</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>197.97817258883279</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1E-4</v>
+      </c>
+      <c r="B38">
+        <v>0.184395579</v>
+      </c>
+      <c r="C38">
+        <v>0.45432517300000003</v>
+      </c>
+      <c r="D38">
+        <v>2.9588832487309809</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>189.85837563451781</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>1E-4</v>
+      </c>
+      <c r="B39">
         <v>0.14647115799999999</v>
       </c>
-      <c r="B11">
+      <c r="C39">
         <v>5.9850028E-2</v>
       </c>
-      <c r="C11">
-        <v>2754.530879864637</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="D39">
+        <v>3.0751269035532829</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>188.44847715736071</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>1E-4</v>
+      </c>
+      <c r="B40">
+        <v>6.2663656999999998E-2</v>
+      </c>
+      <c r="C40">
+        <v>0.30385088799999999</v>
+      </c>
+      <c r="D40">
+        <v>2.5883248730964401</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>162.23959390863021</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>1E-4</v>
+      </c>
+      <c r="B41">
+        <v>0.105007356</v>
+      </c>
+      <c r="C41">
+        <v>0.60413150599999998</v>
+      </c>
+      <c r="D41">
+        <v>3.0664974619289471</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>161.8865482233507</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>1E-4</v>
+      </c>
+      <c r="B42">
         <v>0.547593369</v>
       </c>
-      <c r="B12">
+      <c r="C42">
         <v>7.3545299999999997E-3</v>
       </c>
-      <c r="C12">
-        <v>2741.1950084602372</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13">
+      <c r="D42">
+        <v>5.7817258883248996</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>161.0223350253807</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>1E-4</v>
+      </c>
+      <c r="B43">
         <v>0.12010299200000001</v>
       </c>
-      <c r="B13">
+      <c r="C43">
         <v>1.6509238999999998E-2</v>
       </c>
-      <c r="C13">
-        <v>2735.2593062605761</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14">
+      <c r="D43">
+        <v>2.1421319796954421</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>160.8180203045689</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>1E-4</v>
+      </c>
+      <c r="B44">
         <v>0.38977679199999998</v>
       </c>
-      <c r="B14">
+      <c r="C44">
         <v>0.21193631600000001</v>
       </c>
-      <c r="C14">
-        <v>2730.892131979695</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15">
+      <c r="D44">
+        <v>2.5756345177664808</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>147.07131979695441</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>1E-4</v>
+      </c>
+      <c r="B45">
+        <v>6.2663656999999998E-2</v>
+      </c>
+      <c r="C45">
+        <v>0.30385088799999999</v>
+      </c>
+      <c r="D45">
+        <v>2.0137055837563409</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>145.50050761421321</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>1E-4</v>
+      </c>
+      <c r="B46">
+        <v>0.14647115799999999</v>
+      </c>
+      <c r="C46">
+        <v>5.9850028E-2</v>
+      </c>
+      <c r="D46">
+        <v>3.6670050761421611</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>140.7951776649752</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>1E-4</v>
+      </c>
+      <c r="B47">
+        <v>0.547593369</v>
+      </c>
+      <c r="C47">
+        <v>7.3545299999999997E-3</v>
+      </c>
+      <c r="D47">
+        <v>4.9502538071066198</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>113.9522842639598</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>1E-4</v>
+      </c>
+      <c r="B48">
+        <v>0.38977679199999998</v>
+      </c>
+      <c r="C48">
+        <v>0.21193631600000001</v>
+      </c>
+      <c r="D48">
+        <v>2.7868020304568399</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>110.7766497461931</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>1E-4</v>
+      </c>
+      <c r="B49">
         <v>3.3403383000000002E-2</v>
       </c>
-      <c r="B15">
+      <c r="C49">
         <v>6.6681807999999995E-2</v>
       </c>
-      <c r="C15">
-        <v>2721.5571065989861</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16">
+      <c r="D49">
+        <v>2.1822335025380428</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>108.73756345177689</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>1E-4</v>
+      </c>
+      <c r="B50">
+        <v>3.3403383000000002E-2</v>
+      </c>
+      <c r="C50">
+        <v>6.6681807999999995E-2</v>
+      </c>
+      <c r="D50">
+        <v>2.0857868020304409</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>108.0850253807111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>1E-4</v>
+      </c>
+      <c r="B51">
+        <v>0.12010299200000001</v>
+      </c>
+      <c r="C51">
+        <v>1.6509238999999998E-2</v>
+      </c>
+      <c r="D51">
+        <v>1.769543147208122</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>98.01979695431487</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>1E-4</v>
+      </c>
+      <c r="B52">
+        <v>0.547593369</v>
+      </c>
+      <c r="C52">
+        <v>7.3545299999999997E-3</v>
+      </c>
+      <c r="D52">
+        <v>4.1263959390863008</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>96.209898477157921</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>1E-4</v>
+      </c>
+      <c r="B53">
+        <v>3.3403383000000002E-2</v>
+      </c>
+      <c r="C53">
+        <v>6.6681807999999995E-2</v>
+      </c>
+      <c r="D53">
+        <v>1.707614213197981</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>95.663197969544015</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>1E-4</v>
+      </c>
+      <c r="B54">
+        <v>0.12010299200000001</v>
+      </c>
+      <c r="C54">
+        <v>1.6509238999999998E-2</v>
+      </c>
+      <c r="D54">
+        <v>1.749238578680224</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>95.413959390863795</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>1E-4</v>
+      </c>
+      <c r="B55">
+        <v>0.38977679199999998</v>
+      </c>
+      <c r="C55">
+        <v>0.21193631600000001</v>
+      </c>
+      <c r="D55">
+        <v>2.0527918781725809</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>83.12030456852807</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>1E-4</v>
+      </c>
+      <c r="B56">
+        <v>0.14647115799999999</v>
+      </c>
+      <c r="C56">
+        <v>5.9850028E-2</v>
+      </c>
+      <c r="D56">
+        <v>2.8974619289340389</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>82.336548223350789</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>1E-4</v>
+      </c>
+      <c r="B57">
+        <v>3.3403383000000002E-2</v>
+      </c>
+      <c r="C57">
+        <v>6.6681807999999995E-2</v>
+      </c>
+      <c r="D57">
+        <v>1.7908629441624411</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>70.120050761421808</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>1E-4</v>
+      </c>
+      <c r="B58">
         <v>6.2663656999999998E-2</v>
       </c>
-      <c r="B16">
+      <c r="C58">
         <v>0.30385088799999999</v>
       </c>
-      <c r="C16">
-        <v>2703.8912859560069</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17">
+      <c r="D58">
+        <v>1.5974619289339991</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>64.472842639594305</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>1E-4</v>
+      </c>
+      <c r="B59">
+        <v>6.2663656999999998E-2</v>
+      </c>
+      <c r="C59">
+        <v>0.30385088799999999</v>
+      </c>
+      <c r="D59">
+        <v>1.35532994923858</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>49.901269035532621</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>1E-4</v>
+      </c>
+      <c r="B60">
         <v>4.2312115999999997E-2</v>
       </c>
-      <c r="B17">
+      <c r="C60">
         <v>1.0219173E-2</v>
       </c>
-      <c r="C17">
-        <v>2626.2863790186129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18">
+      <c r="D60">
+        <v>1.088832487309624</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>19.900761421319881</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>1E-4</v>
+      </c>
+      <c r="B61">
+        <v>4.2312115999999997E-2</v>
+      </c>
+      <c r="C61">
+        <v>1.0219173E-2</v>
+      </c>
+      <c r="D61">
+        <v>0.92284263959389889</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>11.87309644670113</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>1E-4</v>
+      </c>
+      <c r="B62">
+        <v>0.547593369</v>
+      </c>
+      <c r="C62">
+        <v>7.3545299999999997E-3</v>
+      </c>
+      <c r="D62">
+        <v>3.5746192893401019</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>-4.8266497461930804</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>1E-4</v>
+      </c>
+      <c r="B63">
+        <v>4.2312115999999997E-2</v>
+      </c>
+      <c r="C63">
+        <v>1.0219173E-2</v>
+      </c>
+      <c r="D63">
+        <v>0.67664974619287932</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>-4.8604060913702156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>1E-4</v>
+      </c>
+      <c r="B64">
+        <v>0.14647115799999999</v>
+      </c>
+      <c r="C64">
+        <v>5.9850028E-2</v>
+      </c>
+      <c r="D64">
+        <v>1.51472081218272</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>-6.2180203045677143</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>1E-4</v>
+      </c>
+      <c r="B65">
+        <v>7.8356125999999998E-2</v>
+      </c>
+      <c r="C65">
+        <v>5.9325649999999999E-3</v>
+      </c>
+      <c r="D65">
+        <v>2.1345177664974422</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>-8.3553299492387527</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>1E-4</v>
+      </c>
+      <c r="B66">
+        <v>4.2312115999999997E-2</v>
+      </c>
+      <c r="C66">
+        <v>1.0219173E-2</v>
+      </c>
+      <c r="D66">
+        <v>0.6350253807106796</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>-13.62614213197925</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>1E-4</v>
+      </c>
+      <c r="B67">
+        <v>1.7800632E-2</v>
+      </c>
+      <c r="C67">
+        <v>8.6187625000000004E-2</v>
+      </c>
+      <c r="D67">
+        <v>0.31725888324874058</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>-35.896192893400517</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>1E-4</v>
+      </c>
+      <c r="B68">
         <v>9.0921470000000001E-3</v>
       </c>
-      <c r="B18">
+      <c r="C68">
         <v>3.4626921999999997E-2</v>
       </c>
-      <c r="C18">
-        <v>2557.819373942471</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19">
+      <c r="D68">
+        <v>0.51675126903554158</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>-49.602538071065297</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>1E-4</v>
+      </c>
+      <c r="B69">
+        <v>9.0921470000000001E-3</v>
+      </c>
+      <c r="C69">
+        <v>3.4626921999999997E-2</v>
+      </c>
+      <c r="D69">
+        <v>0.17918781725888169</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>-51.73807106598953</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>1E-4</v>
+      </c>
+      <c r="B70">
         <v>0.21646782000000001</v>
       </c>
-      <c r="B19">
+      <c r="C70">
         <v>0.150478047</v>
       </c>
-      <c r="C19">
-        <v>2541.4737732656522</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20">
+      <c r="D70">
+        <v>0.27360406091371908</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>-64.529695431471467</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>1E-4</v>
+      </c>
+      <c r="B71">
+        <v>7.8356125999999998E-2</v>
+      </c>
+      <c r="C71">
+        <v>5.9325649999999999E-3</v>
+      </c>
+      <c r="D71">
+        <v>0.81928934010151977</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>-66.160152284263461</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>1E-4</v>
+      </c>
+      <c r="B72">
+        <v>0.21646782000000001</v>
+      </c>
+      <c r="C72">
+        <v>0.150478047</v>
+      </c>
+      <c r="D72">
+        <v>0.32588832487307678</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>-72.90431472081211</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>1E-4</v>
+      </c>
+      <c r="B73">
         <v>1.7800632E-2</v>
       </c>
-      <c r="B20">
+      <c r="C73">
         <v>8.6187625000000004E-2</v>
       </c>
-      <c r="C20">
-        <v>2527.240270727581</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21">
+      <c r="D73">
+        <v>-0.1248730964466986</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>-74.278426395938922</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>1E-4</v>
+      </c>
+      <c r="B74">
+        <v>9.0921470000000001E-3</v>
+      </c>
+      <c r="C74">
+        <v>3.4626921999999997E-2</v>
+      </c>
+      <c r="D74">
+        <v>5.5837563451802907E-2</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>-77.864213197969306</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>1E-4</v>
+      </c>
+      <c r="B75">
         <v>7.8356125999999998E-2</v>
       </c>
-      <c r="B21">
+      <c r="C75">
         <v>5.9325649999999999E-3</v>
       </c>
-      <c r="C21">
-        <v>2521.0871404399331</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22">
+      <c r="D75">
+        <v>0.60812182741120324</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>-84.006598984770889</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>1E-4</v>
+      </c>
+      <c r="B76">
+        <v>9.0921470000000001E-3</v>
+      </c>
+      <c r="C76">
+        <v>3.4626921999999997E-2</v>
+      </c>
+      <c r="D76">
+        <v>-2.5380710659774759E-3</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>-84.161167512689843</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>1E-4</v>
+      </c>
+      <c r="B77">
+        <v>0.21646782000000001</v>
+      </c>
+      <c r="C77">
+        <v>0.150478047</v>
+      </c>
+      <c r="D77">
+        <v>-7.1065989847696187E-2</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>-89.456852791878077</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>1E-4</v>
+      </c>
+      <c r="B78">
+        <v>1.7800632E-2</v>
+      </c>
+      <c r="C78">
+        <v>8.6187625000000004E-2</v>
+      </c>
+      <c r="D78">
+        <v>-0.12131979695432089</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>-93.668527918780867</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>1E-4</v>
+      </c>
+      <c r="B79">
+        <v>1.7800632E-2</v>
+      </c>
+      <c r="C79">
+        <v>8.6187625000000004E-2</v>
+      </c>
+      <c r="D79">
+        <v>-9.238578680204057E-2</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>-102.58807106598989</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>1E-4</v>
+      </c>
+      <c r="B80">
+        <v>0.21646782000000001</v>
+      </c>
+      <c r="C80">
+        <v>0.150478047</v>
+      </c>
+      <c r="D80">
+        <v>-0.25532994923853991</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>-107.05837563451701</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>1E-4</v>
+      </c>
+      <c r="B81">
         <v>0.754085542</v>
       </c>
-      <c r="B22">
+      <c r="C81">
         <v>0.383998434</v>
       </c>
-      <c r="C22">
-        <v>2449.359137055837</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23">
+      <c r="D81">
+        <v>2.283756345177661</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>-111.07588832487239</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>1E-4</v>
+      </c>
+      <c r="B82">
+        <v>7.8356125999999998E-2</v>
+      </c>
+      <c r="C82">
+        <v>5.9325649999999999E-3</v>
+      </c>
+      <c r="D82">
+        <v>5.5329949238583247E-2</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>-139.66852791878131</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>1E-4</v>
+      </c>
+      <c r="B83">
+        <v>0.754085542</v>
+      </c>
+      <c r="C83">
+        <v>0.383998434</v>
+      </c>
+      <c r="D83">
+        <v>1.7015228426395841</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>-151.96040609137069</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>1E-4</v>
+      </c>
+      <c r="B84">
+        <v>0.754085542</v>
+      </c>
+      <c r="C84">
+        <v>0.383998434</v>
+      </c>
+      <c r="D84">
+        <v>1.827918781725923</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>-171.23096446700509</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>1E-4</v>
+      </c>
+      <c r="B85">
+        <v>5.0379819999999999E-2</v>
+      </c>
+      <c r="C85">
+        <v>0.17105295000000001</v>
+      </c>
+      <c r="D85">
+        <v>-0.73705583756346016</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>-174.81472081218249</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>1E-4</v>
+      </c>
+      <c r="B86">
         <v>6.8350249999999998E-3</v>
       </c>
-      <c r="B23">
+      <c r="C86">
         <v>0.85083756399999999</v>
       </c>
-      <c r="C23">
-        <v>2428.1662436548231</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24">
+      <c r="D86">
+        <v>-0.73756345177664073</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>-176.92588832487229</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>1E-4</v>
+      </c>
+      <c r="B87">
+        <v>6.8350249999999998E-3</v>
+      </c>
+      <c r="C87">
+        <v>0.85083756399999999</v>
+      </c>
+      <c r="D87">
+        <v>-0.89137055837561974</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>-177.95558375634499</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>1E-4</v>
+      </c>
+      <c r="B88">
+        <v>0.754085542</v>
+      </c>
+      <c r="C88">
+        <v>0.383998434</v>
+      </c>
+      <c r="D88">
+        <v>1.4928934010152619</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>-180.07360406091351</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>1E-4</v>
+      </c>
+      <c r="B89">
         <v>5.0379819999999999E-2</v>
       </c>
-      <c r="B24">
+      <c r="C89">
         <v>0.17105295000000001</v>
       </c>
-      <c r="C24">
-        <v>2374.6988155668359</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25">
+      <c r="D89">
+        <v>-0.87411167512690113</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>-199.75456852791851</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>1E-4</v>
+      </c>
+      <c r="B90">
+        <v>6.8350249999999998E-3</v>
+      </c>
+      <c r="C90">
+        <v>0.85083756399999999</v>
+      </c>
+      <c r="D90">
+        <v>-1.294923857868</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>-212.537817258883</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>1E-4</v>
+      </c>
+      <c r="B91">
         <v>7.8138310000000002E-3</v>
       </c>
-      <c r="B25">
+      <c r="C91">
         <v>4.2046725E-2</v>
       </c>
-      <c r="C25">
-        <v>2324.0867174280879</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26">
+      <c r="D91">
+        <v>-1.1583756345177569</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>-213.75329949238511</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>1E-4</v>
+      </c>
+      <c r="B92">
+        <v>5.0379819999999999E-2</v>
+      </c>
+      <c r="C92">
+        <v>0.17105295000000001</v>
+      </c>
+      <c r="D92">
+        <v>-1.6203045685278989</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>-253.00558375634449</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>1E-4</v>
+      </c>
+      <c r="B93">
+        <v>2.8560392E-2</v>
+      </c>
+      <c r="C93">
+        <v>0.80790660199999997</v>
+      </c>
+      <c r="D93">
+        <v>-1.475126903553317</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>-256.49263959390811</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>1E-4</v>
+      </c>
+      <c r="B94">
+        <v>7.8138310000000002E-3</v>
+      </c>
+      <c r="C94">
+        <v>4.2046725E-2</v>
+      </c>
+      <c r="D94">
+        <v>-1.526903553299515</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>-265.97385786801999</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>1E-4</v>
+      </c>
+      <c r="B95">
+        <v>6.8350249999999998E-3</v>
+      </c>
+      <c r="C95">
+        <v>0.85083756399999999</v>
+      </c>
+      <c r="D95">
+        <v>-1.4690355329949161</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>-268.69847715736017</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>1E-4</v>
+      </c>
+      <c r="B96">
+        <v>5.0379819999999999E-2</v>
+      </c>
+      <c r="C96">
+        <v>0.17105295000000001</v>
+      </c>
+      <c r="D96">
+        <v>-1.3563451776649591</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>-274.70786802030409</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>1E-4</v>
+      </c>
+      <c r="B97">
+        <v>7.8138310000000002E-3</v>
+      </c>
+      <c r="C97">
+        <v>4.2046725E-2</v>
+      </c>
+      <c r="D97">
+        <v>-1.6832487309644579</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>-295.83172588832463</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>1E-4</v>
+      </c>
+      <c r="B98">
+        <v>5.1710599999999999E-3</v>
+      </c>
+      <c r="C98">
+        <v>5.0245669999999999E-2</v>
+      </c>
+      <c r="D98">
+        <v>-1.4131979695431549</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>-300.20659898477152</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>1E-4</v>
+      </c>
+      <c r="B99">
+        <v>7.8138310000000002E-3</v>
+      </c>
+      <c r="C99">
+        <v>4.2046725E-2</v>
+      </c>
+      <c r="D99">
+        <v>-1.907106598984758</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>-317.33553299492348</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>1E-4</v>
+      </c>
+      <c r="B100">
+        <v>2.0903663999999999E-2</v>
+      </c>
+      <c r="C100">
+        <v>0.66371455700000004</v>
+      </c>
+      <c r="D100">
+        <v>-1.8776649746192751</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>-317.75228426395859</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>1E-4</v>
+      </c>
+      <c r="B101">
         <v>1.0932872999999999E-2</v>
       </c>
-      <c r="B26">
+      <c r="C101">
         <v>2.5693725000000001E-2</v>
       </c>
-      <c r="C26">
-        <v>2284.496615905246</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27">
+      <c r="D101">
+        <v>-1.972081218274099</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>-321.67106598984748</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>1E-4</v>
+      </c>
+      <c r="B102">
         <v>2.8560392E-2</v>
       </c>
-      <c r="B27">
+      <c r="C102">
         <v>0.80790660199999997</v>
       </c>
-      <c r="C27">
-        <v>2275.8337563451778</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28">
+      <c r="D102">
+        <v>-2.008121827411177</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>-322.25177664974558</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>1E-4</v>
+      </c>
+      <c r="B103">
         <v>2.0903663999999999E-2</v>
       </c>
-      <c r="B28">
+      <c r="C103">
         <v>0.66371455700000004</v>
       </c>
-      <c r="C28">
-        <v>2269.7313874788488</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29">
+      <c r="D103">
+        <v>-1.9802030456852791</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>-323.92081218274092</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>1E-4</v>
+      </c>
+      <c r="B104">
+        <v>1.0932872999999999E-2</v>
+      </c>
+      <c r="C104">
+        <v>2.5693725000000001E-2</v>
+      </c>
+      <c r="D104">
+        <v>-1.919289340101521</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>-325.86065989847668</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>1E-4</v>
+      </c>
+      <c r="B105">
         <v>5.1710599999999999E-3</v>
       </c>
-      <c r="B29">
+      <c r="C105">
         <v>5.0245669999999999E-2</v>
       </c>
-      <c r="C29">
-        <v>2229.9302030456861</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30">
+      <c r="D105">
+        <v>-2.2725888324873011</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>-344.73045685279209</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>1E-4</v>
+      </c>
+      <c r="B106">
+        <v>2.8560392E-2</v>
+      </c>
+      <c r="C106">
+        <v>0.80790660199999997</v>
+      </c>
+      <c r="D106">
+        <v>-2.2583756345177801</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>-346.56319796954227</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>1E-4</v>
+      </c>
+      <c r="B107">
+        <v>1.0932872999999999E-2</v>
+      </c>
+      <c r="C107">
+        <v>2.5693725000000001E-2</v>
+      </c>
+      <c r="D107">
+        <v>-2.3766497461928959</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>-351.37842639593867</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>1E-4</v>
+      </c>
+      <c r="B108">
+        <v>2.8560392E-2</v>
+      </c>
+      <c r="C108">
+        <v>0.80790660199999997</v>
+      </c>
+      <c r="D108">
+        <v>-2.2416243654822199</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>-356.27131979695361</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>1E-4</v>
+      </c>
+      <c r="B109">
         <v>2.3822037000000001E-2</v>
       </c>
-      <c r="B30">
+      <c r="C109">
         <v>8.0868999999999996E-2</v>
       </c>
-      <c r="C30">
-        <v>2203.3726734348561</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31">
+      <c r="D109">
+        <v>-2.6010152284263768</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>-379.05406091370548</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>1E-4</v>
+      </c>
+      <c r="B110">
+        <v>5.1710599999999999E-3</v>
+      </c>
+      <c r="C110">
+        <v>5.0245669999999999E-2</v>
+      </c>
+      <c r="D110">
+        <v>-2.492893401015237</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>-393.55710659898432</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>1E-4</v>
+      </c>
+      <c r="B111">
+        <v>2.0903663999999999E-2</v>
+      </c>
+      <c r="C111">
+        <v>0.66371455700000004</v>
+      </c>
+      <c r="D111">
+        <v>-2.470050761421319</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>-401.73375634517743</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>1E-4</v>
+      </c>
+      <c r="B112">
+        <v>2.3822037000000001E-2</v>
+      </c>
+      <c r="C112">
+        <v>8.0868999999999996E-2</v>
+      </c>
+      <c r="D112">
+        <v>-2.6822335025380788</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>-409.72157360406038</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>1E-4</v>
+      </c>
+      <c r="B113">
+        <v>2.0903663999999999E-2</v>
+      </c>
+      <c r="C113">
+        <v>0.66371455700000004</v>
+      </c>
+      <c r="D113">
+        <v>-2.6081218274112001</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>-416.44974619289297</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>1E-4</v>
+      </c>
+      <c r="B114">
+        <v>5.1710599999999999E-3</v>
+      </c>
+      <c r="C114">
+        <v>5.0245669999999999E-2</v>
+      </c>
+      <c r="D114">
+        <v>-2.7329949238578588</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>-423.71294416243649</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>1E-4</v>
+      </c>
+      <c r="B115">
+        <v>1.0932872999999999E-2</v>
+      </c>
+      <c r="C115">
+        <v>2.5693725000000001E-2</v>
+      </c>
+      <c r="D115">
+        <v>-2.7147208121827622</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>-424.83477157360392</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>1E-4</v>
+      </c>
+      <c r="B116">
         <v>1.544101E-2</v>
       </c>
-      <c r="B31">
+      <c r="C116">
         <v>1.3004618000000001E-2</v>
       </c>
-      <c r="C31">
-        <v>2121.6188663282578</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32">
+      <c r="D116">
+        <v>-2.9604060913705581</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>-444.50253807106628</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>1E-4</v>
+      </c>
+      <c r="B117">
+        <v>2.3822037000000001E-2</v>
+      </c>
+      <c r="C117">
+        <v>8.0868999999999996E-2</v>
+      </c>
+      <c r="D117">
+        <v>-3.2025380710659772</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>-452.64517766497431</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>1E-4</v>
+      </c>
+      <c r="B118">
+        <v>1.544101E-2</v>
+      </c>
+      <c r="C118">
+        <v>1.3004618000000001E-2</v>
+      </c>
+      <c r="D118">
+        <v>-3.2294416243654571</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>-488.75076142131928</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>1E-4</v>
+      </c>
+      <c r="B119">
+        <v>1.544101E-2</v>
+      </c>
+      <c r="C119">
+        <v>1.3004618000000001E-2</v>
+      </c>
+      <c r="D119">
+        <v>-3.4192893401015181</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>-489.73274111675062</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>1E-4</v>
+      </c>
+      <c r="B120">
         <v>1.3004537E-2</v>
       </c>
-      <c r="B32">
+      <c r="C120">
         <v>8.7338229999999999E-3</v>
       </c>
-      <c r="C32">
-        <v>2054.0626057529612</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33">
+      <c r="D120">
+        <v>-3.4319796954314579</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>-491.86928934010149</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>1E-4</v>
+      </c>
+      <c r="B121">
+        <v>2.3822037000000001E-2</v>
+      </c>
+      <c r="C121">
+        <v>8.0868999999999996E-2</v>
+      </c>
+      <c r="D121">
+        <v>-3.2025380710659799</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>-495.58401015228412</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>1E-4</v>
+      </c>
+      <c r="B122">
+        <v>1.544101E-2</v>
+      </c>
+      <c r="C122">
+        <v>1.3004618000000001E-2</v>
+      </c>
+      <c r="D122">
+        <v>-3.5725888324873201</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>-508.38654822335019</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>1E-4</v>
+      </c>
+      <c r="B123">
+        <v>1.3004537E-2</v>
+      </c>
+      <c r="C123">
+        <v>8.7338229999999999E-3</v>
+      </c>
+      <c r="D123">
+        <v>-3.731472081218278</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>-531.15939086294372</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>1E-4</v>
+      </c>
+      <c r="B124">
         <v>8.8879412000000005E-2</v>
       </c>
-      <c r="B33">
+      <c r="C124">
         <v>2.8582090000000001E-2</v>
       </c>
-      <c r="C33">
-        <v>2038.370558375635</v>
+      <c r="D124">
+        <v>-4.0888324873096424</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>-566.6652284263954</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>1E-4</v>
+      </c>
+      <c r="B125">
+        <v>1.3004537E-2</v>
+      </c>
+      <c r="C125">
+        <v>8.7338229999999999E-3</v>
+      </c>
+      <c r="D125">
+        <v>-4.0467005076142186</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>-570.6746192893404</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>1E-4</v>
+      </c>
+      <c r="B126">
+        <v>8.8879412000000005E-2</v>
+      </c>
+      <c r="C126">
+        <v>2.8582090000000001E-2</v>
+      </c>
+      <c r="D126">
+        <v>-4.2025380710659768</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>-579.55507614213207</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>1E-4</v>
+      </c>
+      <c r="B127">
+        <v>1.3004537E-2</v>
+      </c>
+      <c r="C127">
+        <v>8.7338229999999999E-3</v>
+      </c>
+      <c r="D127">
+        <v>-4.2152284263959388</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>-587.85888324873031</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>1E-4</v>
+      </c>
+      <c r="B128">
+        <v>8.8879412000000005E-2</v>
+      </c>
+      <c r="C128">
+        <v>2.8582090000000001E-2</v>
+      </c>
+      <c r="D128">
+        <v>-4.291878172588838</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>-590.53020304568497</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>1E-4</v>
+      </c>
+      <c r="B129">
+        <v>8.8879412000000005E-2</v>
+      </c>
+      <c r="C129">
+        <v>2.8582090000000001E-2</v>
+      </c>
+      <c r="D129">
+        <v>-4.8903553299492204</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>-657.64923857868018</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C33">
-    <sortCondition descending="1" ref="C1:C33"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G129">
+    <sortCondition descending="1" ref="G1:G129"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/May_5_full_log/LHS_HRP_0.0001_res.xlsx
+++ b/May_5_full_log/LHS_HRP_0.0001_res.xlsx
@@ -8,14 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharm\Blueness\May_5_full_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0665090A-9275-4080-9CC4-81CABAC9394B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA382AB-3854-44FA-8DE0-F4879DDA3490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -448,10 +459,10 @@
         <v>8.1243654822335003</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.97500781005935755</v>
       </c>
       <c r="G2">
         <v>568.6532994923864</v>
@@ -471,10 +482,10 @@
         <v>6.5401015228426402</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>0.56302521008403361</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.97727413846631617</v>
       </c>
       <c r="G3">
         <v>514.80101522842722</v>
@@ -494,10 +505,10 @@
         <v>7.0284263959391069</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.43697478991596639</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>0.9717607973421919</v>
       </c>
       <c r="G4">
         <v>492.30786802030491</v>
@@ -517,10 +528,10 @@
         <v>7.4857868020304608</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>0.40336134453781508</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>0.99121177188580578</v>
       </c>
       <c r="G5">
         <v>480.19314720812162</v>
@@ -540,10 +551,10 @@
         <v>6.2218274111675029</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>0.48739495798319332</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.96509749530880395</v>
       </c>
       <c r="G6">
         <v>465.62918781725909</v>
@@ -563,10 +574,10 @@
         <v>5.6040609137055668</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>0.56302521008403361</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.96838768115942253</v>
       </c>
       <c r="G7">
         <v>457.93477157360451</v>
@@ -586,10 +597,10 @@
         <v>7.5873096446700643</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>0.38655462184873951</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>0.97442965143506932</v>
       </c>
       <c r="G8">
         <v>454.10329949238599</v>
@@ -609,10 +620,10 @@
         <v>6.5274111675127173</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.39495798319327741</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.93235865930476736</v>
       </c>
       <c r="G9">
         <v>448.74873096446748</v>
@@ -632,10 +643,10 @@
         <v>7.4081218274111862</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>0.38655462184873951</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.97523639851993793</v>
       </c>
       <c r="G10">
         <v>446.87817258883331</v>
@@ -655,10 +666,10 @@
         <v>5.9664974619289204</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.46218487394957991</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.99098179343202419</v>
       </c>
       <c r="G11">
         <v>445.11015228426402</v>
@@ -678,10 +689,10 @@
         <v>7.2192893401015246</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.38655462184873951</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.98305442272535626</v>
       </c>
       <c r="G12">
         <v>433.94619289340119</v>
@@ -701,10 +712,10 @@
         <v>5.3786802030456968</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.68907563025210083</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.96281615704039247</v>
       </c>
       <c r="G13">
         <v>428.40329949238662</v>
@@ -724,10 +735,10 @@
         <v>5.6614213197969647</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>0.43697478991596639</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>0.97991571774410635</v>
       </c>
       <c r="G14">
         <v>393.85406091370572</v>
@@ -747,10 +758,10 @@
         <v>6.6167512690355386</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>0.38655462184873951</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.97704641350211041</v>
       </c>
       <c r="G15">
         <v>379.37385786802088</v>
@@ -770,10 +781,10 @@
         <v>7.6020304568527806</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>0.25210084033613439</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>0.97541399572649667</v>
       </c>
       <c r="G16">
         <v>376.34314720812188</v>
@@ -793,10 +804,10 @@
         <v>5.4979695431472244</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>0.96338288246699311</v>
       </c>
       <c r="G17">
         <v>365.79644670050823</v>
@@ -839,10 +850,10 @@
         <v>6.1426395939086396</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>0.31932773109243701</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>0.99221551937856334</v>
       </c>
       <c r="G19">
         <v>346.40812182741172</v>
@@ -931,10 +942,10 @@
         <v>6.7335025380710816</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>0.32773109243697468</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>0.99007915567282401</v>
       </c>
       <c r="G23">
         <v>314.97182741116751</v>
@@ -1092,10 +1103,10 @@
         <v>6.309137055837585</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>0.30252100840336138</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>0.98965323034837849</v>
       </c>
       <c r="G30">
         <v>259.41675126903613</v>
@@ -1207,10 +1218,10 @@
         <v>6.1817258883248591</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>0.24369747899159669</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>0.93752668746920831</v>
       </c>
       <c r="G35">
         <v>215.18426395939119</v>
@@ -1368,10 +1379,10 @@
         <v>5.7817258883248996</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>0.2352941176470589</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>0.98811237928006901</v>
       </c>
       <c r="G42">
         <v>161.0223350253807</v>
